--- a/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>17-26</t>
+    <t>P7-26</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1239,16 +1239,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="H11" s="5">
         <v>0.28</v>
       </c>
       <c r="I11" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="J11" s="8">
-        <v>10.13</v>
+        <v>25.24</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1271,7 +1271,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="G12" s="9">
         <v>9.25</v>
@@ -1280,10 +1280,10 @@
         <v>0.08</v>
       </c>
       <c r="I12" s="9">
-        <v>6.38</v>
+        <v>2.1</v>
       </c>
       <c r="J12" s="8">
-        <v>76.56</v>
+        <v>25.2</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="G2" s="5">
         <v>0.28</v>
       </c>
       <c r="H2" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="I2" s="8">
-        <v>10.13</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="F3" s="9">
         <v>9.25</v>
@@ -1756,10 +1756,10 @@
         <v>0.08</v>
       </c>
       <c r="H3" s="9">
-        <v>6.38</v>
+        <v>2.1</v>
       </c>
       <c r="I3" s="8">
-        <v>76.56</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">

--- a/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-26</t>
+    <t>17-26</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -1239,16 +1239,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="H11" s="5">
         <v>0.28</v>
       </c>
       <c r="I11" s="5">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="J11" s="8">
-        <v>25.24</v>
+        <v>10.13</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1271,7 +1271,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="G12" s="9">
         <v>9.25</v>
@@ -1280,10 +1280,10 @@
         <v>0.08</v>
       </c>
       <c r="I12" s="9">
-        <v>2.1</v>
+        <v>6.38</v>
       </c>
       <c r="J12" s="8">
-        <v>25.2</v>
+        <v>76.56</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="G2" s="5">
         <v>0.28</v>
       </c>
       <c r="H2" s="5">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="I2" s="8">
-        <v>25.24</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>7.15</v>
+        <v>2.87</v>
       </c>
       <c r="F3" s="9">
         <v>9.25</v>
@@ -1756,10 +1756,10 @@
         <v>0.08</v>
       </c>
       <c r="H3" s="9">
-        <v>2.1</v>
+        <v>6.38</v>
       </c>
       <c r="I3" s="8">
-        <v>25.2</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">

--- a/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
+++ b/SGC-CKN/Excel/97090c79-afdf-43c0-8930-eed52108a3f0_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_17-26_D800_17-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>17-26</t>
+    <t>P7-26</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>
@@ -196,7 +196,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:49
@@ -1239,16 +1239,16 @@
         <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="H11" s="5">
         <v>0.28</v>
       </c>
       <c r="I11" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="J11" s="8">
-        <v>10.13</v>
+        <v>25.24</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1271,7 +1271,7 @@
         <v>34</v>
       </c>
       <c r="F12" s="9">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="G12" s="9">
         <v>9.25</v>
@@ -1280,10 +1280,10 @@
         <v>0.08</v>
       </c>
       <c r="I12" s="9">
-        <v>6.38</v>
+        <v>2.1</v>
       </c>
       <c r="J12" s="8">
-        <v>76.56</v>
+        <v>25.2</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1721,16 +1721,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="G2" s="5">
         <v>0.28</v>
       </c>
       <c r="H2" s="5">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="I2" s="8">
-        <v>10.13</v>
+        <v>25.24</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>2.87</v>
+        <v>7.15</v>
       </c>
       <c r="F3" s="9">
         <v>9.25</v>
@@ -1756,10 +1756,10 @@
         <v>0.08</v>
       </c>
       <c r="H3" s="9">
-        <v>6.38</v>
+        <v>2.1</v>
       </c>
       <c r="I3" s="8">
-        <v>76.56</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
